--- a/hardware/txe8116-module/fabrication/bom/txe8116-module_rev_v1.0.0-bom.xlsx
+++ b/hardware/txe8116-module/fabrication/bom/txe8116-module_rev_v1.0.0-bom.xlsx
@@ -119,7 +119,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-03-24_19-54-47</t>
+    <t>2026-03-24_20-05-20</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/hardware/txe8116-module/fabrication/bom/txe8116-module_rev_v1.0.0-bom.xlsx
+++ b/hardware/txe8116-module/fabrication/bom/txe8116-module_rev_v1.0.0-bom.xlsx
@@ -119,7 +119,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-03-24_20-05-20</t>
+    <t>2026-03-24_20-18-04</t>
   </si>
   <si>
     <t>KiCad Version:</t>
